--- a/PathPointsDefine.xlsx
+++ b/PathPointsDefine.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProjects\c550\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84802BF-2E49-47CF-8849-DB3CFFD7C4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3520FC-2092-4BFE-9C31-1D5F8FE42342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{60BF1A9E-F77C-4FB5-BF3B-E5EC594AA92E}"/>
+    <workbookView xWindow="4665" yWindow="225" windowWidth="19725" windowHeight="15210" activeTab="2" xr2:uid="{60BF1A9E-F77C-4FB5-BF3B-E5EC594AA92E}"/>
   </bookViews>
   <sheets>
     <sheet name="PathPoints6" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="仿真" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="164">
   <si>
     <t>命令形式</t>
   </si>
@@ -563,6 +564,66 @@
   </si>
   <si>
     <t>p3 伸缩</t>
+  </si>
+  <si>
+    <t>扩展命令</t>
+  </si>
+  <si>
+    <t>1=猫道</t>
+  </si>
+  <si>
+    <t>2=顶驱</t>
+  </si>
+  <si>
+    <t>3=铁钻工</t>
+  </si>
+  <si>
+    <t>X=1仿真</t>
+  </si>
+  <si>
+    <t>上升</t>
+  </si>
+  <si>
+    <t>判断上升</t>
+  </si>
+  <si>
+    <t>下降</t>
+  </si>
+  <si>
+    <t>判断下降</t>
+  </si>
+  <si>
+    <t>打开</t>
+  </si>
+  <si>
+    <t>关闭</t>
+  </si>
+  <si>
+    <t>伸出到井口位置</t>
+  </si>
+  <si>
+    <t>伸出到鼠洞位置</t>
+  </si>
+  <si>
+    <t>缩回到井口位置</t>
+  </si>
+  <si>
+    <t>缩回到鼠洞位置</t>
+  </si>
+  <si>
+    <t>判断伸出到井口位置</t>
+  </si>
+  <si>
+    <t>判断伸出到鼠洞位置</t>
+  </si>
+  <si>
+    <t>判断缩回到井口位置</t>
+  </si>
+  <si>
+    <t>判断缩回到鼠洞位置</t>
+  </si>
+  <si>
+    <t>4=直接发送Z数据</t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479670DE-A070-4E78-B924-40F346BFE3B4}">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.25" style="26" customWidth="1"/>
@@ -3078,6 +3139,14 @@
       </c>
       <c r="F45" s="4" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="4">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3390,4 +3459,156 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85A9C4B-DE89-45EC-BD64-B70BD29F9A6E}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C4">
+        <v>-1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C5">
+        <v>-2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C7">
+        <v>-1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C12">
+        <v>-1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C13">
+        <v>-2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C14">
+        <v>-3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C15">
+        <v>-4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PathPointsDefine.xlsx
+++ b/PathPointsDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProjects\c550\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3520FC-2092-4BFE-9C31-1D5F8FE42342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF83519-0E1C-4010-9A99-374EBB27ED13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4665" yWindow="225" windowWidth="19725" windowHeight="15210" activeTab="2" xr2:uid="{60BF1A9E-F77C-4FB5-BF3B-E5EC594AA92E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="165">
   <si>
     <t>命令形式</t>
   </si>
@@ -624,6 +624,9 @@
   </si>
   <si>
     <t>4=直接发送Z数据</t>
+  </si>
+  <si>
+    <t>5=抓取的钻杆数量为Z</t>
   </si>
 </sst>
 </file>
@@ -1389,18 +1392,39 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1408,27 +1432,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1829,21 +1832,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A1" s="39"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="37" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="31" t="s">
         <v>123</v>
       </c>
       <c r="L1" s="2"/>
@@ -1855,21 +1858,21 @@
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" s="39"/>
+      <c r="A2" s="33"/>
       <c r="B2" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="38"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="32"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1879,20 +1882,20 @@
       <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A3" s="39"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
       <c r="K3" s="12" t="s">
         <v>119</v>
       </c>
@@ -1907,7 +1910,7 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A4" s="39"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2061,7 +2064,7 @@
       <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="30" t="s">
         <v>82</v>
       </c>
       <c r="D7" s="2"/>
@@ -2089,7 +2092,7 @@
       <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" s="28"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="9" t="s">
@@ -2117,7 +2120,7 @@
       <c r="B9" s="6">
         <v>3</v>
       </c>
-      <c r="C9" s="28"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="10" t="s">
         <v>65</v>
       </c>
@@ -2147,7 +2150,7 @@
       <c r="B10" s="6">
         <v>4</v>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="9" t="s">
@@ -2175,7 +2178,7 @@
       <c r="B11" s="6">
         <v>5</v>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="9" t="s">
@@ -2203,7 +2206,7 @@
       <c r="B12" s="6">
         <v>6</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="9" t="s">
@@ -2225,13 +2228,13 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="30">
         <v>8</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="16" t="s">
         <v>65</v>
       </c>
@@ -2263,18 +2266,18 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="40"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="41" t="s">
+      <c r="A14" s="35"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2285,13 +2288,13 @@
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="30">
         <v>9</v>
       </c>
-      <c r="C15" s="28"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="16" t="s">
         <v>65</v>
       </c>
@@ -2323,16 +2326,16 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="40"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2343,18 +2346,18 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="40"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="41" t="s">
+      <c r="A17" s="35"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2371,7 +2374,7 @@
       <c r="B18" s="6">
         <v>14</v>
       </c>
-      <c r="C18" s="28"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9" t="s">
@@ -2395,13 +2398,13 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="37">
         <v>15</v>
       </c>
-      <c r="C19" s="28"/>
+      <c r="C19" s="30"/>
       <c r="D19" s="16" t="s">
         <v>65</v>
       </c>
@@ -2429,18 +2432,18 @@
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="41" t="s">
+      <c r="A20" s="29"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2457,7 +2460,7 @@
       <c r="B21" s="15">
         <v>16</v>
       </c>
-      <c r="C21" s="28"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="14"/>
       <c r="E21" s="10" t="s">
         <v>65</v>
@@ -2493,7 +2496,7 @@
       <c r="B22" s="6">
         <v>11</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="11" t="s">
@@ -2521,7 +2524,7 @@
       <c r="B23" s="6">
         <v>21</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="37" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="2"/>
@@ -2547,16 +2550,16 @@
       <c r="B24" s="6">
         <v>91</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="28" t="s">
+      <c r="C24" s="39"/>
+      <c r="D24" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2573,16 +2576,16 @@
       <c r="B25" s="6">
         <v>92</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="28" t="s">
+      <c r="C25" s="39"/>
+      <c r="D25" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2599,16 +2602,16 @@
       <c r="B26" s="6">
         <v>93</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="28" t="s">
+      <c r="C26" s="39"/>
+      <c r="D26" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2625,16 +2628,16 @@
       <c r="B27" s="15">
         <v>31</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="34" t="s">
+      <c r="C27" s="39"/>
+      <c r="D27" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
@@ -2651,14 +2654,14 @@
       <c r="B28" s="6">
         <v>32</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2675,7 +2678,7 @@
       <c r="B29" s="6">
         <v>33</v>
       </c>
-      <c r="C29" s="32"/>
+      <c r="C29" s="39"/>
       <c r="D29" s="9" t="s">
         <v>96</v>
       </c>
@@ -2707,7 +2710,7 @@
       <c r="B30" s="6">
         <v>35</v>
       </c>
-      <c r="C30" s="32"/>
+      <c r="C30" s="39"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -2731,7 +2734,7 @@
       <c r="B31" s="6">
         <v>36</v>
       </c>
-      <c r="C31" s="32"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2749,13 +2752,13 @@
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="35" t="s">
+      <c r="A32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="37">
         <v>37</v>
       </c>
-      <c r="C32" s="32"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="9" t="s">
         <v>96</v>
       </c>
@@ -2783,9 +2786,9 @@
       <c r="R32" s="2"/>
     </row>
     <row r="33" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="36"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="32"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
       <c r="D33" s="21"/>
       <c r="E33" s="11" t="s">
         <v>116</v>
@@ -2817,7 +2820,7 @@
       <c r="B34" s="6">
         <v>22</v>
       </c>
-      <c r="C34" s="32"/>
+      <c r="C34" s="39"/>
       <c r="D34" s="11" t="s">
         <v>99</v>
       </c>
@@ -2844,7 +2847,7 @@
       <c r="B35" s="6">
         <v>23</v>
       </c>
-      <c r="C35" s="32"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="11" t="s">
         <v>99</v>
       </c>
@@ -2871,7 +2874,7 @@
       <c r="B36" s="6">
         <v>24</v>
       </c>
-      <c r="C36" s="32"/>
+      <c r="C36" s="39"/>
       <c r="D36" s="11" t="s">
         <v>102</v>
       </c>
@@ -2901,7 +2904,7 @@
       <c r="B37" s="6">
         <v>25</v>
       </c>
-      <c r="C37" s="32"/>
+      <c r="C37" s="39"/>
       <c r="D37" s="11" t="s">
         <v>102</v>
       </c>
@@ -2931,7 +2934,7 @@
       <c r="B38" s="6">
         <v>26</v>
       </c>
-      <c r="C38" s="32"/>
+      <c r="C38" s="39"/>
       <c r="D38" s="11" t="s">
         <v>104</v>
       </c>
@@ -2967,7 +2970,7 @@
       <c r="B39" s="6">
         <v>27</v>
       </c>
-      <c r="C39" s="32"/>
+      <c r="C39" s="39"/>
       <c r="D39" s="11" t="s">
         <v>104</v>
       </c>
@@ -3001,7 +3004,7 @@
       <c r="B40" s="6">
         <v>28</v>
       </c>
-      <c r="C40" s="32"/>
+      <c r="C40" s="39"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -3025,7 +3028,7 @@
       <c r="B41" s="6">
         <v>38</v>
       </c>
-      <c r="C41" s="32"/>
+      <c r="C41" s="39"/>
       <c r="D41" s="11" t="s">
         <v>110</v>
       </c>
@@ -3051,7 +3054,7 @@
       <c r="B42" s="15">
         <v>41</v>
       </c>
-      <c r="C42" s="32"/>
+      <c r="C42" s="39"/>
       <c r="D42" s="11" t="s">
         <v>133</v>
       </c>
@@ -3081,7 +3084,7 @@
       <c r="B43" s="6">
         <v>42</v>
       </c>
-      <c r="C43" s="32"/>
+      <c r="C43" s="39"/>
       <c r="D43" s="11" t="s">
         <v>131</v>
       </c>
@@ -3151,6 +3154,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="C23:C43"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D27:J27"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="D25:J25"/>
     <mergeCell ref="K1:K2"/>
@@ -3167,14 +3178,6 @@
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="D20:J20"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="C23:C43"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="D27:J27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3463,10 +3466,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85A9C4B-DE89-45EC-BD64-B70BD29F9A6E}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="18.25" customWidth="1"/>
   </cols>
@@ -3608,6 +3611,11 @@
         <v>163</v>
       </c>
     </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B17" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
